--- a/results/BECCS_scenario_city.xlsx
+++ b/results/BECCS_scenario_city.xlsx
@@ -479,7 +479,7 @@
         <v>9.9562749</v>
       </c>
       <c r="F2" t="n">
-        <v>9.9562749</v>
+        <v>10.475809</v>
       </c>
     </row>
     <row r="3">
@@ -523,7 +523,7 @@
         <v>17.732548</v>
       </c>
       <c r="F4" t="n">
-        <v>17.732548</v>
+        <v>4.3363931</v>
       </c>
     </row>
     <row r="5">
@@ -545,7 +545,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.95412964</v>
       </c>
     </row>
     <row r="6">
@@ -564,10 +564,10 @@
         <v>4.7264983</v>
       </c>
       <c r="E6" t="n">
-        <v>5.5621829</v>
+        <v>4.7264983</v>
       </c>
       <c r="F6" t="n">
-        <v>5.5621829</v>
+        <v>4.7264983</v>
       </c>
     </row>
     <row r="7">
@@ -611,7 +611,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.068374015</v>
       </c>
     </row>
     <row r="9">
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2.6250172</v>
       </c>
     </row>
     <row r="10">
@@ -655,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.43743929</v>
       </c>
     </row>
     <row r="11">
@@ -677,7 +677,7 @@
         <v>0.62306863</v>
       </c>
       <c r="F11" t="n">
-        <v>0.62306863</v>
+        <v>0.028513479</v>
       </c>
     </row>
     <row r="12">
@@ -699,7 +699,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2.7816753</v>
       </c>
     </row>
     <row r="13">
@@ -721,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>14.425803</v>
       </c>
     </row>
     <row r="14">
@@ -737,7 +737,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.10063605</v>
+        <v>0.10060635</v>
       </c>
       <c r="E14" t="n">
         <v>0.10063605</v>
@@ -765,7 +765,7 @@
         <v>6.4710648</v>
       </c>
       <c r="F15" t="n">
-        <v>6.4710648</v>
+        <v>3.9729046</v>
       </c>
     </row>
     <row r="16">
@@ -806,10 +806,10 @@
         <v>4.3231462</v>
       </c>
       <c r="E17" t="n">
-        <v>41.185619</v>
+        <v>36.451556</v>
       </c>
       <c r="F17" t="n">
-        <v>41.185619</v>
+        <v>4.3231462</v>
       </c>
     </row>
     <row r="18">
@@ -853,7 +853,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.4310931</v>
       </c>
     </row>
     <row r="20">
@@ -919,7 +919,7 @@
         <v>16.476025</v>
       </c>
       <c r="F22" t="n">
-        <v>16.476025</v>
+        <v>4.5349884</v>
       </c>
     </row>
     <row r="23">
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.21303356</v>
       </c>
     </row>
     <row r="25">
@@ -985,7 +985,7 @@
         <v>10.449785</v>
       </c>
       <c r="F25" t="n">
-        <v>10.449785</v>
+        <v>5.3970803</v>
       </c>
     </row>
     <row r="26">
@@ -1026,10 +1026,10 @@
         <v>5.1157253</v>
       </c>
       <c r="E27" t="n">
-        <v>14.402735</v>
+        <v>14.187494</v>
       </c>
       <c r="F27" t="n">
-        <v>14.402735</v>
+        <v>5.1157253</v>
       </c>
     </row>
     <row r="28">
@@ -1051,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.31359375</v>
       </c>
     </row>
     <row r="29">
@@ -1073,7 +1073,7 @@
         <v>3.6817844</v>
       </c>
       <c r="F29" t="n">
-        <v>3.6817844</v>
+        <v>3.749591</v>
       </c>
     </row>
     <row r="30">
@@ -1095,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>9.9541948</v>
       </c>
     </row>
     <row r="31">
@@ -1117,7 +1117,7 @@
         <v>8.5061695</v>
       </c>
       <c r="F31" t="n">
-        <v>8.5061695</v>
+        <v>7.310138</v>
       </c>
     </row>
     <row r="32">
@@ -1161,7 +1161,7 @@
         <v>0.90030193</v>
       </c>
       <c r="F33" t="n">
-        <v>0.90030193</v>
+        <v>1.8648443</v>
       </c>
     </row>
     <row r="34">
@@ -1183,7 +1183,7 @@
         <v>4.9519611</v>
       </c>
       <c r="F34" t="n">
-        <v>4.9519611</v>
+        <v>4.5126277</v>
       </c>
     </row>
     <row r="35">
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.9179121099999999</v>
       </c>
     </row>
     <row r="37">
@@ -1268,10 +1268,10 @@
         <v>1.402577</v>
       </c>
       <c r="E38" t="n">
-        <v>4.0893177</v>
+        <v>2.5357633</v>
       </c>
       <c r="F38" t="n">
-        <v>4.0893177</v>
+        <v>2.5357633</v>
       </c>
     </row>
     <row r="39">
@@ -1293,7 +1293,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1.5438293</v>
       </c>
     </row>
     <row r="40">
@@ -1315,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1.0046447</v>
       </c>
     </row>
     <row r="41">
@@ -1337,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>0.13218344</v>
       </c>
     </row>
     <row r="42">
@@ -1356,10 +1356,10 @@
         <v>0.92157316</v>
       </c>
       <c r="E42" t="n">
-        <v>7.2214512</v>
+        <v>0.92157316</v>
       </c>
       <c r="F42" t="n">
-        <v>7.2214512</v>
+        <v>0.92157316</v>
       </c>
     </row>
     <row r="43">
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>2.9038134</v>
       </c>
     </row>
     <row r="45">
@@ -1444,10 +1444,10 @@
         <v>4.5459636</v>
       </c>
       <c r="E46" t="n">
-        <v>4.5459636</v>
+        <v>5.6810048</v>
       </c>
       <c r="F46" t="n">
-        <v>4.5459636</v>
+        <v>5.6810048</v>
       </c>
     </row>
     <row r="47">
@@ -1488,10 +1488,10 @@
         <v>1.5355595</v>
       </c>
       <c r="E48" t="n">
-        <v>5.8350315</v>
+        <v>1.5355595</v>
       </c>
       <c r="F48" t="n">
-        <v>5.8350315</v>
+        <v>1.5355595</v>
       </c>
     </row>
     <row r="49">
@@ -1513,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>6.0322377</v>
       </c>
     </row>
     <row r="50">
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>0.0266247</v>
       </c>
     </row>
     <row r="52">
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>0.91947649</v>
       </c>
     </row>
     <row r="54">
@@ -1645,7 +1645,7 @@
         <v>2.8830897</v>
       </c>
       <c r="F55" t="n">
-        <v>2.8830897</v>
+        <v>2.862821</v>
       </c>
     </row>
     <row r="56">
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>4.0909127</v>
       </c>
     </row>
     <row r="58">
@@ -1752,10 +1752,10 @@
         <v>0.43210422</v>
       </c>
       <c r="E60" t="n">
-        <v>6.1543973</v>
+        <v>6.2591918</v>
       </c>
       <c r="F60" t="n">
-        <v>6.1543973</v>
+        <v>0.43210422</v>
       </c>
     </row>
     <row r="61">
@@ -1777,7 +1777,7 @@
         <v>18.756256</v>
       </c>
       <c r="F61" t="n">
-        <v>18.756256</v>
+        <v>3.9148117</v>
       </c>
     </row>
     <row r="62">
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>0.42018847</v>
       </c>
     </row>
     <row r="63">
@@ -1821,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>4.9739622</v>
       </c>
     </row>
     <row r="64">
@@ -1843,7 +1843,7 @@
         <v>32.808749</v>
       </c>
       <c r="F64" t="n">
-        <v>32.808749</v>
+        <v>24.584287</v>
       </c>
     </row>
     <row r="65">
@@ -1865,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>2.1960051</v>
       </c>
     </row>
     <row r="66">
@@ -1884,10 +1884,10 @@
         <v>0.97403379</v>
       </c>
       <c r="E66" t="n">
-        <v>0.97922743</v>
+        <v>1.1944685</v>
       </c>
       <c r="F66" t="n">
-        <v>0.97922743</v>
+        <v>0.97403379</v>
       </c>
     </row>
     <row r="67">
@@ -1909,7 +1909,7 @@
         <v>11.887403</v>
       </c>
       <c r="F67" t="n">
-        <v>11.887403</v>
+        <v>2.8627759</v>
       </c>
     </row>
     <row r="68">
@@ -1931,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1.2967733</v>
       </c>
     </row>
     <row r="69">
@@ -1944,7 +1944,7 @@
         <v>0.75692534</v>
       </c>
       <c r="C69" t="n">
-        <v>36.01683</v>
+        <v>36.016811</v>
       </c>
       <c r="D69" t="n">
         <v>0.75692534</v>
@@ -1975,7 +1975,7 @@
         <v>19.279744</v>
       </c>
       <c r="F70" t="n">
-        <v>19.279744</v>
+        <v>19.31616</v>
       </c>
     </row>
     <row r="71">
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>6.189905</v>
       </c>
     </row>
     <row r="72">
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>8.8609083</v>
       </c>
     </row>
     <row r="73">
@@ -2041,7 +2041,7 @@
         <v>5.1279366</v>
       </c>
       <c r="F73" t="n">
-        <v>5.1279366</v>
+        <v>2.42107</v>
       </c>
     </row>
     <row r="74">
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>2.6958756</v>
       </c>
     </row>
     <row r="75">
@@ -2085,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>0.75585265</v>
       </c>
     </row>
     <row r="76">
@@ -2129,7 +2129,7 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>11.684859</v>
       </c>
     </row>
     <row r="78">
@@ -2151,7 +2151,7 @@
         <v>3.1713728</v>
       </c>
       <c r="F78" t="n">
-        <v>3.1713728</v>
+        <v>2.1378291</v>
       </c>
     </row>
     <row r="79">
@@ -2173,7 +2173,7 @@
         <v>3.0231369</v>
       </c>
       <c r="F79" t="n">
-        <v>3.0231369</v>
+        <v>0.33245499</v>
       </c>
     </row>
     <row r="80">
@@ -2195,7 +2195,7 @@
         <v>1.5663941</v>
       </c>
       <c r="F80" t="n">
-        <v>1.5663941</v>
+        <v>4.3094639</v>
       </c>
     </row>
     <row r="81">
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1.5243928</v>
       </c>
     </row>
     <row r="83">
@@ -2261,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>10.724821</v>
       </c>
     </row>
     <row r="84">
@@ -2283,7 +2283,7 @@
         <v>26.522943</v>
       </c>
       <c r="F84" t="n">
-        <v>26.522943</v>
+        <v>4.5532981</v>
       </c>
     </row>
     <row r="85">
@@ -2305,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>4.136484</v>
       </c>
     </row>
     <row r="86">
@@ -2349,7 +2349,7 @@
         <v>11.058235</v>
       </c>
       <c r="F87" t="n">
-        <v>11.058235</v>
+        <v>4.4749015</v>
       </c>
     </row>
     <row r="88">
@@ -2371,7 +2371,7 @@
         <v>3.5727137</v>
       </c>
       <c r="F88" t="n">
-        <v>3.5727137</v>
+        <v>3.4476111</v>
       </c>
     </row>
     <row r="89">
@@ -2393,7 +2393,7 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>4.748677</v>
       </c>
     </row>
     <row r="90">
@@ -2437,7 +2437,7 @@
         <v>43.951649</v>
       </c>
       <c r="F91" t="n">
-        <v>43.951649</v>
+        <v>1.9256633</v>
       </c>
     </row>
     <row r="92">
@@ -2459,7 +2459,7 @@
         <v>12.32736</v>
       </c>
       <c r="F92" t="n">
-        <v>12.32736</v>
+        <v>3.1990216</v>
       </c>
     </row>
     <row r="93">
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>4.1207352</v>
       </c>
     </row>
     <row r="94">
@@ -2613,7 +2613,7 @@
         <v>5.2988583</v>
       </c>
       <c r="F99" t="n">
-        <v>5.2988583</v>
+        <v>4.3919513</v>
       </c>
     </row>
     <row r="100">
@@ -2635,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>6.7556921</v>
       </c>
     </row>
     <row r="101">
@@ -2657,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>5.382425</v>
       </c>
     </row>
     <row r="102">
@@ -2679,7 +2679,7 @@
         <v>12.512937</v>
       </c>
       <c r="F102" t="n">
-        <v>12.512937</v>
+        <v>2.4356064</v>
       </c>
     </row>
     <row r="103">
@@ -2723,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>3.4689142</v>
       </c>
     </row>
     <row r="105">
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>2.0630095</v>
       </c>
     </row>
     <row r="107">
@@ -2789,7 +2789,7 @@
         <v>11.019678</v>
       </c>
       <c r="F107" t="n">
-        <v>11.019678</v>
+        <v>7.0145653</v>
       </c>
     </row>
     <row r="108">
@@ -2808,10 +2808,10 @@
         <v>1.4298156</v>
       </c>
       <c r="E108" t="n">
-        <v>2.7265889</v>
+        <v>1.4298156</v>
       </c>
       <c r="F108" t="n">
-        <v>2.7265889</v>
+        <v>1.4298156</v>
       </c>
     </row>
     <row r="109">
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>7.1845534</v>
       </c>
     </row>
     <row r="110">
@@ -2874,10 +2874,10 @@
         <v>1.3050585</v>
       </c>
       <c r="E111" t="n">
-        <v>3.2353108</v>
+        <v>4.7888652</v>
       </c>
       <c r="F111" t="n">
-        <v>3.2353108</v>
+        <v>4.7888652</v>
       </c>
     </row>
     <row r="112">
@@ -2899,7 +2899,7 @@
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>0.52618113</v>
       </c>
     </row>
     <row r="113">
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>5.6665531</v>
       </c>
     </row>
     <row r="114">
@@ -2965,7 +2965,7 @@
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>2.2179317</v>
       </c>
     </row>
     <row r="116">
@@ -2987,7 +2987,7 @@
         <v>25.368485</v>
       </c>
       <c r="F116" t="n">
-        <v>25.368485</v>
+        <v>10.053835</v>
       </c>
     </row>
     <row r="117">
@@ -3031,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>1.2629958</v>
       </c>
     </row>
     <row r="119">
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>6.2262566</v>
       </c>
     </row>
     <row r="120">
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>9.5324691</v>
       </c>
     </row>
     <row r="121">
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>0.13903698</v>
       </c>
     </row>
     <row r="122">
@@ -3119,7 +3119,7 @@
         <v>6.0562259</v>
       </c>
       <c r="F122" t="n">
-        <v>6.0562259</v>
+        <v>3.196822</v>
       </c>
     </row>
     <row r="123">
@@ -3185,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>1.3064468</v>
       </c>
     </row>
     <row r="126">
@@ -3207,7 +3207,7 @@
         <v>6.1671731</v>
       </c>
       <c r="F126" t="n">
-        <v>6.1671731</v>
+        <v>7.6208917</v>
       </c>
     </row>
     <row r="127">
@@ -3226,10 +3226,10 @@
         <v>4.8107102</v>
       </c>
       <c r="E127" t="n">
-        <v>7.6789225</v>
+        <v>4.8107102</v>
       </c>
       <c r="F127" t="n">
-        <v>7.6789225</v>
+        <v>4.8107102</v>
       </c>
     </row>
     <row r="128">
@@ -3251,7 +3251,7 @@
         <v>10.325614</v>
       </c>
       <c r="F128" t="n">
-        <v>10.325614</v>
+        <v>3.8217091</v>
       </c>
     </row>
     <row r="129">
@@ -3273,7 +3273,7 @@
         <v>0.054712224</v>
       </c>
       <c r="F129" t="n">
-        <v>0.054712224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>5.9876089</v>
       </c>
     </row>
     <row r="133">
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>2.4419955</v>
       </c>
     </row>
     <row r="135">
@@ -3405,7 +3405,7 @@
         <v>3.3050003</v>
       </c>
       <c r="F135" t="n">
-        <v>3.3050003</v>
+        <v>3.8673753</v>
       </c>
     </row>
     <row r="136">
@@ -3424,10 +3424,10 @@
         <v>3.5252228</v>
       </c>
       <c r="E136" t="n">
-        <v>7.8854803</v>
+        <v>5.9354838</v>
       </c>
       <c r="F136" t="n">
-        <v>7.8854803</v>
+        <v>5.9354838</v>
       </c>
     </row>
     <row r="137">
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>4.945983</v>
       </c>
     </row>
     <row r="138">
@@ -3493,7 +3493,7 @@
         <v>21.363401</v>
       </c>
       <c r="F139" t="n">
-        <v>21.363401</v>
+        <v>2.8282466</v>
       </c>
     </row>
     <row r="140">
@@ -3515,7 +3515,7 @@
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>2.2213708</v>
       </c>
     </row>
     <row r="141">
@@ -3537,7 +3537,7 @@
         <v>5.8736031</v>
       </c>
       <c r="F141" t="n">
-        <v>5.8736031</v>
+        <v>2.2094938</v>
       </c>
     </row>
     <row r="142">
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>1.9021395</v>
       </c>
     </row>
     <row r="144">
@@ -3603,7 +3603,7 @@
         <v>8.3715762</v>
       </c>
       <c r="F144" t="n">
-        <v>8.3715762</v>
+        <v>4.0449711</v>
       </c>
     </row>
     <row r="145">
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>3.6459453</v>
       </c>
     </row>
     <row r="149">
@@ -3713,7 +3713,7 @@
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>2.7191002</v>
       </c>
     </row>
     <row r="150">
@@ -3757,7 +3757,7 @@
         <v>5.5268016</v>
       </c>
       <c r="F151" t="n">
-        <v>5.5268016</v>
+        <v>4.2295156</v>
       </c>
     </row>
     <row r="152">
@@ -3820,10 +3820,10 @@
         <v>5.5574996</v>
       </c>
       <c r="E154" t="n">
-        <v>32.686856</v>
+        <v>47.712673</v>
       </c>
       <c r="F154" t="n">
-        <v>32.686856</v>
+        <v>5.5574996</v>
       </c>
     </row>
     <row r="155">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>1.2204546</v>
       </c>
     </row>
     <row r="156">
@@ -3867,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>2.3386982</v>
       </c>
     </row>
     <row r="157">
@@ -3908,10 +3908,10 @@
         <v>4.7497235</v>
       </c>
       <c r="E158" t="n">
-        <v>6.5926528</v>
+        <v>5.4576116</v>
       </c>
       <c r="F158" t="n">
-        <v>6.5926528</v>
+        <v>5.4576116</v>
       </c>
     </row>
     <row r="159">
@@ -3955,7 +3955,7 @@
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>0.054712224</v>
       </c>
     </row>
     <row r="161">
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>5.4792266</v>
       </c>
     </row>
     <row r="165">
@@ -4065,7 +4065,7 @@
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>4.9539092</v>
       </c>
     </row>
     <row r="166">
@@ -4153,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>0</v>
+        <v>5.5792287</v>
       </c>
     </row>
     <row r="170">
@@ -4175,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>0</v>
+        <v>3.1079096</v>
       </c>
     </row>
     <row r="171">
@@ -4219,7 +4219,7 @@
         <v>1.0478106</v>
       </c>
       <c r="F172" t="n">
-        <v>1.0478106</v>
+        <v>6.4468354</v>
       </c>
     </row>
     <row r="173">
@@ -4241,7 +4241,7 @@
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>0</v>
+        <v>6.4365932</v>
       </c>
     </row>
     <row r="174">
@@ -4263,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
+        <v>6.6801745</v>
       </c>
     </row>
     <row r="175">
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>0</v>
+        <v>0.73664823</v>
       </c>
     </row>
     <row r="176">
@@ -4304,10 +4304,10 @@
         <v>0.1301722</v>
       </c>
       <c r="E176" t="n">
-        <v>1.1966845</v>
+        <v>0.50215655</v>
       </c>
       <c r="F176" t="n">
-        <v>1.1966845</v>
+        <v>0.1301722</v>
       </c>
     </row>
     <row r="177">
@@ -4351,7 +4351,7 @@
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>0</v>
+        <v>3.8300518</v>
       </c>
     </row>
     <row r="179">
@@ -4373,7 +4373,7 @@
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>0</v>
+        <v>2.616352</v>
       </c>
     </row>
     <row r="180">
@@ -4395,7 +4395,7 @@
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>0</v>
+        <v>5.3691609</v>
       </c>
     </row>
     <row r="181">
@@ -4417,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>0</v>
+        <v>4.8766536</v>
       </c>
     </row>
     <row r="182">
@@ -4483,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>0</v>
+        <v>2.9217977</v>
       </c>
     </row>
     <row r="185">
@@ -4505,7 +4505,7 @@
         <v>12.493879</v>
       </c>
       <c r="F185" t="n">
-        <v>12.493879</v>
+        <v>3.3658995</v>
       </c>
     </row>
     <row r="186">
@@ -4527,7 +4527,7 @@
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>0</v>
+        <v>1.2972859</v>
       </c>
     </row>
     <row r="187">
@@ -4546,10 +4546,10 @@
         <v>2.1083424</v>
       </c>
       <c r="E187" t="n">
-        <v>2.1083424</v>
+        <v>8.408220500000001</v>
       </c>
       <c r="F187" t="n">
-        <v>2.1083424</v>
+        <v>8.408220500000001</v>
       </c>
     </row>
     <row r="188">
@@ -4593,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>0</v>
+        <v>5.4637287</v>
       </c>
     </row>
     <row r="190">
@@ -4615,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>0</v>
+        <v>3.4584816</v>
       </c>
     </row>
     <row r="191">
@@ -4659,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>0</v>
+        <v>11.111227</v>
       </c>
     </row>
     <row r="193">
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>0</v>
+        <v>1.5365613</v>
       </c>
     </row>
     <row r="197">
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>0</v>
+        <v>9.0734762</v>
       </c>
     </row>
     <row r="198">
@@ -4791,7 +4791,7 @@
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>0</v>
+        <v>1.8088551</v>
       </c>
     </row>
     <row r="199">
@@ -4901,7 +4901,7 @@
         <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>0</v>
+        <v>7.9985459</v>
       </c>
     </row>
     <row r="204">
@@ -4945,7 +4945,7 @@
         <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>0</v>
+        <v>0.13322492</v>
       </c>
     </row>
     <row r="206">
@@ -4967,7 +4967,7 @@
         <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>0</v>
+        <v>0.80186519</v>
       </c>
     </row>
     <row r="207">
@@ -4986,10 +4986,10 @@
         <v>9.2410801</v>
       </c>
       <c r="E207" t="n">
-        <v>9.572431699999999</v>
+        <v>12.726403</v>
       </c>
       <c r="F207" t="n">
-        <v>9.572431699999999</v>
+        <v>12.726403</v>
       </c>
     </row>
     <row r="208">
@@ -5011,7 +5011,7 @@
         <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>0</v>
+        <v>2.1287193</v>
       </c>
     </row>
     <row r="209">
@@ -5033,7 +5033,7 @@
         <v>0</v>
       </c>
       <c r="F209" t="n">
-        <v>0</v>
+        <v>12.38085</v>
       </c>
     </row>
     <row r="210">
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="F210" t="n">
-        <v>0</v>
+        <v>1.6521801</v>
       </c>
     </row>
     <row r="211">
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="F212" t="n">
-        <v>0</v>
+        <v>0.22499623</v>
       </c>
     </row>
     <row r="213">
@@ -5121,7 +5121,7 @@
         <v>0</v>
       </c>
       <c r="F213" t="n">
-        <v>0</v>
+        <v>5.3988179</v>
       </c>
     </row>
     <row r="214">
@@ -5143,7 +5143,7 @@
         <v>0</v>
       </c>
       <c r="F214" t="n">
-        <v>0</v>
+        <v>0.10479443</v>
       </c>
     </row>
     <row r="215">
@@ -5187,7 +5187,7 @@
         <v>7.3367613</v>
       </c>
       <c r="F216" t="n">
-        <v>7.3367613</v>
+        <v>3.0511629</v>
       </c>
     </row>
     <row r="217">
@@ -5231,7 +5231,7 @@
         <v>7.1485837</v>
       </c>
       <c r="F218" t="n">
-        <v>7.1485837</v>
+        <v>1.9082101</v>
       </c>
     </row>
     <row r="219">
@@ -5253,7 +5253,7 @@
         <v>5.5531649</v>
       </c>
       <c r="F219" t="n">
-        <v>5.5531649</v>
+        <v>5.5808108</v>
       </c>
     </row>
     <row r="220">
@@ -5272,10 +5272,10 @@
         <v>4.3743953</v>
       </c>
       <c r="E220" t="n">
-        <v>7.052719</v>
+        <v>6.2258829</v>
       </c>
       <c r="F220" t="n">
-        <v>7.052719</v>
+        <v>6.0868459</v>
       </c>
     </row>
     <row r="221">
@@ -5297,7 +5297,7 @@
         <v>0</v>
       </c>
       <c r="F221" t="n">
-        <v>0</v>
+        <v>7.5849159</v>
       </c>
     </row>
     <row r="222">
@@ -5319,7 +5319,7 @@
         <v>0.7805415</v>
       </c>
       <c r="F222" t="n">
-        <v>0.7805415</v>
+        <v>0.46694775</v>
       </c>
     </row>
     <row r="223">
@@ -5363,7 +5363,7 @@
         <v>1.4777275</v>
       </c>
       <c r="F224" t="n">
-        <v>1.4777275</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -5385,7 +5385,7 @@
         <v>0</v>
       </c>
       <c r="F225" t="n">
-        <v>0</v>
+        <v>0.97766928</v>
       </c>
     </row>
     <row r="226">
@@ -5407,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="F226" t="n">
-        <v>0</v>
+        <v>1.9519522</v>
       </c>
     </row>
     <row r="227">
@@ -5451,7 +5451,7 @@
         <v>9.3540636</v>
       </c>
       <c r="F228" t="n">
-        <v>9.3540636</v>
+        <v>5.0898158</v>
       </c>
     </row>
     <row r="229">
@@ -5473,7 +5473,7 @@
         <v>0</v>
       </c>
       <c r="F229" t="n">
-        <v>0</v>
+        <v>2.6858151</v>
       </c>
     </row>
     <row r="230">
@@ -5517,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="F231" t="n">
-        <v>0</v>
+        <v>11.336658</v>
       </c>
     </row>
     <row r="232">
@@ -5561,7 +5561,7 @@
         <v>12.151621</v>
       </c>
       <c r="F233" t="n">
-        <v>12.151621</v>
+        <v>1.8732471</v>
       </c>
     </row>
     <row r="234">
@@ -5583,7 +5583,7 @@
         <v>4.2797501</v>
       </c>
       <c r="F234" t="n">
-        <v>4.2797501</v>
+        <v>2.9475929</v>
       </c>
     </row>
     <row r="235">
@@ -5605,7 +5605,7 @@
         <v>0.5105525400000001</v>
       </c>
       <c r="F235" t="n">
-        <v>0.5105525400000001</v>
+        <v>9.202711900000001</v>
       </c>
     </row>
     <row r="236">
@@ -5627,7 +5627,7 @@
         <v>0</v>
       </c>
       <c r="F236" t="n">
-        <v>0</v>
+        <v>2.4132418</v>
       </c>
     </row>
     <row r="237">
@@ -5671,7 +5671,7 @@
         <v>2.6119876</v>
       </c>
       <c r="F238" t="n">
-        <v>2.6119876</v>
+        <v>2.3215348</v>
       </c>
     </row>
     <row r="239">
@@ -5693,7 +5693,7 @@
         <v>3.2042959</v>
       </c>
       <c r="F239" t="n">
-        <v>3.2042959</v>
+        <v>9.9903704</v>
       </c>
     </row>
     <row r="240">
@@ -5715,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="F240" t="n">
-        <v>0</v>
+        <v>0.37198435</v>
       </c>
     </row>
     <row r="241">
@@ -5737,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="F241" t="n">
-        <v>0</v>
+        <v>1.6294256</v>
       </c>
     </row>
     <row r="242">
@@ -5759,7 +5759,7 @@
         <v>0</v>
       </c>
       <c r="F242" t="n">
-        <v>0</v>
+        <v>5.6191345</v>
       </c>
     </row>
     <row r="243">
@@ -5869,7 +5869,7 @@
         <v>15.47503</v>
       </c>
       <c r="F247" t="n">
-        <v>15.47503</v>
+        <v>12.677161</v>
       </c>
     </row>
     <row r="248">
@@ -5891,7 +5891,7 @@
         <v>1.8272525</v>
       </c>
       <c r="F248" t="n">
-        <v>1.8272525</v>
+        <v>2.9843255</v>
       </c>
     </row>
     <row r="249">
@@ -5913,7 +5913,7 @@
         <v>0</v>
       </c>
       <c r="F249" t="n">
-        <v>0</v>
+        <v>2.039929</v>
       </c>
     </row>
     <row r="250">
@@ -5932,10 +5932,10 @@
         <v>4.0307953</v>
       </c>
       <c r="E250" t="n">
-        <v>4.5920516</v>
+        <v>5.4188877</v>
       </c>
       <c r="F250" t="n">
-        <v>4.5920516</v>
+        <v>5.4188877</v>
       </c>
     </row>
     <row r="251">
@@ -5957,7 +5957,7 @@
         <v>0</v>
       </c>
       <c r="F251" t="n">
-        <v>0</v>
+        <v>2.7288097</v>
       </c>
     </row>
     <row r="252">
@@ -5979,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="F252" t="n">
-        <v>0</v>
+        <v>3.6836434</v>
       </c>
     </row>
     <row r="253">
@@ -6023,7 +6023,7 @@
         <v>11.852164</v>
       </c>
       <c r="F254" t="n">
-        <v>11.852164</v>
+        <v>9.480528400000001</v>
       </c>
     </row>
     <row r="255">
@@ -6089,7 +6089,7 @@
         <v>0</v>
       </c>
       <c r="F257" t="n">
-        <v>0</v>
+        <v>5.2641994</v>
       </c>
     </row>
     <row r="258">
@@ -6111,7 +6111,7 @@
         <v>0</v>
       </c>
       <c r="F258" t="n">
-        <v>0</v>
+        <v>4.0023236</v>
       </c>
     </row>
     <row r="259">
@@ -6155,7 +6155,7 @@
         <v>0</v>
       </c>
       <c r="F260" t="n">
-        <v>0</v>
+        <v>3.0477798</v>
       </c>
     </row>
     <row r="261">
@@ -6196,10 +6196,10 @@
         <v>0.92106559</v>
       </c>
       <c r="E262" t="n">
-        <v>5.9338091</v>
+        <v>8.1298142</v>
       </c>
       <c r="F262" t="n">
-        <v>5.9338091</v>
+        <v>0.92106559</v>
       </c>
     </row>
     <row r="263">
@@ -6221,7 +6221,7 @@
         <v>0</v>
       </c>
       <c r="F263" t="n">
-        <v>0</v>
+        <v>0.16952911</v>
       </c>
     </row>
     <row r="264">
@@ -6240,10 +6240,10 @@
         <v>0.4398934</v>
       </c>
       <c r="E264" t="n">
-        <v>1.7028892</v>
+        <v>0.58164699</v>
       </c>
       <c r="F264" t="n">
-        <v>1.7028892</v>
+        <v>0.4398934</v>
       </c>
     </row>
     <row r="265">
@@ -6284,10 +6284,10 @@
         <v>2.1643474</v>
       </c>
       <c r="E266" t="n">
-        <v>11.852532</v>
+        <v>11.480262</v>
       </c>
       <c r="F266" t="n">
-        <v>11.852532</v>
+        <v>6.9406731</v>
       </c>
     </row>
     <row r="267">
@@ -6309,7 +6309,7 @@
         <v>0</v>
       </c>
       <c r="F267" t="n">
-        <v>0</v>
+        <v>0.37460167</v>
       </c>
     </row>
     <row r="268">
@@ -6353,7 +6353,7 @@
         <v>0</v>
       </c>
       <c r="F269" t="n">
-        <v>0</v>
+        <v>2.8381963</v>
       </c>
     </row>
     <row r="270">
@@ -6372,10 +6372,10 @@
         <v>0.68464102</v>
       </c>
       <c r="E270" t="n">
-        <v>0.78943545</v>
+        <v>0.68464102</v>
       </c>
       <c r="F270" t="n">
-        <v>0.78943545</v>
+        <v>0.68464102</v>
       </c>
     </row>
     <row r="271">
@@ -6419,7 +6419,7 @@
         <v>8.5114657</v>
       </c>
       <c r="F272" t="n">
-        <v>8.5114657</v>
+        <v>0.63491217</v>
       </c>
     </row>
     <row r="273">
@@ -6441,7 +6441,7 @@
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>0.56005213</v>
       </c>
     </row>
     <row r="274">
@@ -6463,7 +6463,7 @@
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>0.52009437</v>
       </c>
     </row>
     <row r="275">
@@ -6485,7 +6485,7 @@
         <v>56.148396</v>
       </c>
       <c r="F275" t="n">
-        <v>56.148396</v>
+        <v>2.3333618</v>
       </c>
     </row>
     <row r="276">
@@ -6507,7 +6507,7 @@
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>1.6485572</v>
       </c>
     </row>
     <row r="277">
@@ -6529,7 +6529,7 @@
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>1.8028996</v>
       </c>
     </row>
     <row r="278">
@@ -6551,7 +6551,7 @@
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>25.501504</v>
       </c>
     </row>
     <row r="279">
@@ -6573,7 +6573,7 @@
         <v>5.1108137</v>
       </c>
       <c r="F279" t="n">
-        <v>5.1108137</v>
+        <v>3.107197</v>
       </c>
     </row>
     <row r="280">
@@ -6595,7 +6595,7 @@
         <v>13.216259</v>
       </c>
       <c r="F280" t="n">
-        <v>13.216259</v>
+        <v>3.8264743</v>
       </c>
     </row>
     <row r="281">
@@ -6617,7 +6617,7 @@
         <v>8.258452</v>
       </c>
       <c r="F281" t="n">
-        <v>8.258452</v>
+        <v>5.084976</v>
       </c>
     </row>
     <row r="282">
@@ -6639,7 +6639,7 @@
         <v>0</v>
       </c>
       <c r="F282" t="n">
-        <v>0</v>
+        <v>5.8695813</v>
       </c>
     </row>
     <row r="283">
@@ -6658,10 +6658,10 @@
         <v>3.8967356</v>
       </c>
       <c r="E283" t="n">
-        <v>3.8967356</v>
+        <v>4.2280872</v>
       </c>
       <c r="F283" t="n">
-        <v>3.8967356</v>
+        <v>4.2280872</v>
       </c>
     </row>
     <row r="284">
@@ -6705,7 +6705,7 @@
         <v>10.89725</v>
       </c>
       <c r="F285" t="n">
-        <v>10.89725</v>
+        <v>0.48175656</v>
       </c>
     </row>
     <row r="286">
@@ -6727,7 +6727,7 @@
         <v>0</v>
       </c>
       <c r="F286" t="n">
-        <v>0</v>
+        <v>6.7257416</v>
       </c>
     </row>
     <row r="287">
@@ -6746,10 +6746,10 @@
         <v>0.06566451099999999</v>
       </c>
       <c r="E287" t="n">
-        <v>3.2551448</v>
+        <v>5.0709149</v>
       </c>
       <c r="F287" t="n">
-        <v>3.2551448</v>
+        <v>0.06566451099999999</v>
       </c>
     </row>
     <row r="288">
@@ -6771,7 +6771,7 @@
         <v>3.0500509</v>
       </c>
       <c r="F288" t="n">
-        <v>3.0500509</v>
+        <v>0.84464948</v>
       </c>
     </row>
     <row r="289">
@@ -6793,7 +6793,7 @@
         <v>0</v>
       </c>
       <c r="F289" t="n">
-        <v>0</v>
+        <v>7.8191891</v>
       </c>
     </row>
     <row r="290">
@@ -6815,7 +6815,7 @@
         <v>0</v>
       </c>
       <c r="F290" t="n">
-        <v>0</v>
+        <v>3.0480239</v>
       </c>
     </row>
     <row r="291">
@@ -6859,7 +6859,7 @@
         <v>0</v>
       </c>
       <c r="F292" t="n">
-        <v>0</v>
+        <v>0.89719972</v>
       </c>
     </row>
     <row r="293">
@@ -6903,7 +6903,7 @@
         <v>4.5115769</v>
       </c>
       <c r="F294" t="n">
-        <v>4.5115769</v>
+        <v>4.6071321</v>
       </c>
     </row>
     <row r="295">
@@ -6925,7 +6925,7 @@
         <v>0</v>
       </c>
       <c r="F295" t="n">
-        <v>0</v>
+        <v>1.1453409</v>
       </c>
     </row>
     <row r="296">
@@ -6966,10 +6966,10 @@
         <v>1.0004986</v>
       </c>
       <c r="E297" t="n">
-        <v>8.395463400000001</v>
+        <v>5.580117</v>
       </c>
       <c r="F297" t="n">
-        <v>8.395463400000001</v>
+        <v>5.580117</v>
       </c>
     </row>
     <row r="298">
@@ -6991,7 +6991,7 @@
         <v>10.851344</v>
       </c>
       <c r="F298" t="n">
-        <v>10.851344</v>
+        <v>4.6640343</v>
       </c>
     </row>
     <row r="299">
@@ -7013,7 +7013,7 @@
         <v>0</v>
       </c>
       <c r="F299" t="n">
-        <v>0</v>
+        <v>1.337397</v>
       </c>
     </row>
     <row r="300">
@@ -7098,10 +7098,10 @@
         <v>2.3711665</v>
       </c>
       <c r="E303" t="n">
-        <v>3.9064926</v>
+        <v>2.3711665</v>
       </c>
       <c r="F303" t="n">
-        <v>3.9064926</v>
+        <v>2.3711665</v>
       </c>
     </row>
     <row r="304">
@@ -7123,7 +7123,7 @@
         <v>0</v>
       </c>
       <c r="F304" t="n">
-        <v>0</v>
+        <v>10.115764</v>
       </c>
     </row>
     <row r="305">
